--- a/xlsx_files/2025_추가급여.xlsx
+++ b/xlsx_files/2025_추가급여.xlsx
@@ -19,159 +19,303 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="170">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="171">
+  <x:si>
+    <x:t>1등급취약가구_바형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급취약가구_마형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2등급취약가구_가형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증1인가구_라형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가족의직장생활_마형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급1인가구_마형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급1인가구_다형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가족의직장생활_나형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증1인가구_가형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급1인가구_바형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증1인가구_바형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급1인가구_라형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2등급1인가구_가형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증1인가구_마형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증취약가구_마형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급1인가구_가형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급1인가구_나형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증1인가구_다형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2등급1인가구_나형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2등급1인가구_바형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증취약가구_가형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2등급1인가구_마형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급취약가구_나형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증취약가구_바형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2등급1인가구_라형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급취약가구_라형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2등급이하취약가구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증취약가구_다형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2등급이하1인가구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증취약가구_나형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2등급취약가구_나형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급취약가구_다형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2등급1인가구_다형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증취약가구_라형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급취약가구_가형</x:t>
+  </x:si>
   <x:si>
     <x:t>2등급취약가구_다형</x:t>
   </x:si>
   <x:si>
+    <x:t>2등급취약가구_라형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보호자일시부재_가형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보호자일시부재_바형</x:t>
+  </x:si>
+  <x:si>
     <x:t>2등급취약가구_마형</x:t>
   </x:si>
   <x:si>
+    <x:t>보호자일시부재_나형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보호자일시부재_라형</x:t>
+  </x:si>
+  <x:si>
     <x:t>2등급취약가구_바형</x:t>
   </x:si>
   <x:si>
-    <x:t>2등급취약가구_라형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보호자일시부재_나형</x:t>
-  </x:si>
-  <x:si>
     <x:t>보호자일시부재_다형</x:t>
   </x:si>
   <x:si>
-    <x:t>보호자일시부재_가형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보호자일시부재_라형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보호자일시부재_바형</x:t>
+    <x:t>가족의직장생활_가형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증1인가구여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가족의직장생활_다형</x:t>
   </x:si>
   <x:si>
     <x:t>보호자일시부재_마형</x:t>
   </x:si>
   <x:si>
-    <x:t>가족의직장생활_가형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가족의직장생활_다형</x:t>
-  </x:si>
-  <x:si>
     <x:t>가족의직장생활_라형</x:t>
   </x:si>
   <x:si>
-    <x:t>최중증1인가구여부</x:t>
-  </x:si>
-  <x:si>
     <x:t>가족의직장생활_바형</x:t>
   </x:si>
   <x:si>
     <x:t>최중증1인가구_나형</x:t>
   </x:si>
   <x:si>
-    <x:t>최중증1인가구_다형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최중증1인가구_가형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가족의직장생활_나형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가족의직장생활_마형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급1인가구_마형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급1인가구_바형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급1인가구_가형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최중증1인가구_바형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급1인가구_다형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급1인가구_라형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2등급1인가구_가형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최중증1인가구_마형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최중증1인가구_라형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급1인가구_나형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최중증취약가구_마형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2등급1인가구_나형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2등급1인가구_라형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2등급1인가구_마형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2등급1인가구_다형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최중증취약가구_가형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2등급1인가구_바형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최중증취약가구_나형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최중증취약가구_다형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최중증취약가구_라형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2등급이하1인가구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2등급이하취약가구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급취약가구_나형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급취약가구_가형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급취약가구_라형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2등급취약가구_나형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최중증취약가구_바형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급취약가구_다형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급취약가구_바형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급취약가구_마형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2등급취약가구_가형</x:t>
+    <x:t>기준중위소득70%초과~120%이하</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A103</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급취약가구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A099</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소득구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기초수급자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>학교생활_가형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>등급구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출산가구_바형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직장생활_라형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직장생활_다형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정부지원금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>추가급여구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>학교생활_바형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>학교생활여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출산가구_마형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출산가구_가형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A037</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출산가구여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출산가구_나형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자립준비_다형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본인부담금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직장생활_마형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출산가구_다형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출산가구_라형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>학교생활_마형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자립준비_가형</x:t>
   </x:si>
   <x:si>
     <x:t>전국가구평균소득50%이하</x:t>
@@ -180,346 +324,205 @@
     <x:t>순번</x:t>
   </x:si>
   <x:si>
+    <x:t>지원량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>차상위</x:t>
+  </x:si>
+  <x:si>
     <x:t>등급명</x:t>
   </x:si>
   <x:si>
-    <x:t>차상위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지원량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A029</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소득구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>등급구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기초수급자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학교생활_가형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출산가구_바형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학교생활여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출산가구여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>본인부담금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출산가구_가형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>추가급여구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출산가구_다형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출산가구_마형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출산가구_나형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출산가구_라형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정부지원금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직장생활_마형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학교생활_마형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자립준비_가형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자립준비_다형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A037</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직장생활_라형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직장생활_다형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A042</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학교생활_바형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A039</x:t>
+    <x:t>A080</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A085</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A086</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A072</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A079</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A063</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A078</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A075</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A076</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1등급1인가구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A077</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자립준비_마형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A070</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A064</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A084</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자립준비_바형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A067</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가족의직장생활</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A073</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A061</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A090</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최중증취약가구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A088</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A069</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A074</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A105</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A071</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A065</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자립준비_라형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자립준비여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직장생활여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A045</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A038</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A066</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직장생활_나형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>학교생활_라형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>학교생활_다형</x:t>
   </x:si>
   <x:si>
     <x:t>자립준비_나형</x:t>
   </x:si>
   <x:si>
-    <x:t>학교생활_다형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자립준비여부</x:t>
+    <x:t>A041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A047</x:t>
   </x:si>
   <x:si>
     <x:t>직장생활_바형</x:t>
   </x:si>
   <x:si>
-    <x:t>A045</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자립준비_라형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직장생활_나형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직장생활여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학교생활_라형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A038</x:t>
+    <x:t>학교생활_나형</x:t>
   </x:si>
   <x:si>
     <x:t>직장생활_가형</x:t>
   </x:si>
   <x:si>
-    <x:t>A033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학교생활_나형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A066</x:t>
-  </x:si>
-  <x:si>
     <x:t>보호자일시부재</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A076</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A077</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A063</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A078</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급1인가구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A075</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A072</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A079</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A080</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A085</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A086</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A071</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A069</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A084</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A074</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A065</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자립준비_바형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A061</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가족의직장생활</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A070</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자립준비_마형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A062</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A064</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A067</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A073</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A104</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A090</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최중증취약가구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A105</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A088</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A107</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A103</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1등급취약가구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A099</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A106</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A108</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A095</x:t>
   </x:si>
   <x:si>
     <x:t>전국가구평균소득50%초과~100%이하</x:t>
@@ -1485,28 +1488,28 @@
   <x:sheetData>
     <x:row r="1" spans="1:8">
       <x:c r="A1" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -1514,10 +1517,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>70</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D2" s="4">
         <x:v>1332000</x:v>
@@ -1529,10 +1532,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G2" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8">
@@ -1540,10 +1543,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="7" t="s">
-        <x:v>71</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C3" s="8" t="s">
-        <x:v>75</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D3" s="9">
         <x:v>1332000</x:v>
@@ -1555,10 +1558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="10" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H3" s="11" t="s">
-        <x:v>66</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
@@ -1566,10 +1569,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="8" t="s">
-        <x:v>72</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C4" s="8" t="s">
-        <x:v>73</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D4" s="9">
         <x:v>1332000</x:v>
@@ -1581,10 +1584,10 @@
         <x:v>26600</x:v>
       </x:c>
       <x:c r="G4" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H4" s="11" t="s">
-        <x:v>66</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
@@ -1592,10 +1595,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C5" s="8" t="s">
-        <x:v>76</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D5" s="9">
         <x:v>1332000</x:v>
@@ -1607,10 +1610,10 @@
         <x:v>39900</x:v>
       </x:c>
       <x:c r="G5" s="10" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H5" s="11" t="s">
-        <x:v>66</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
@@ -1618,10 +1621,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="8" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C6" s="8" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D6" s="9">
         <x:v>1332000</x:v>
@@ -1633,10 +1636,10 @@
         <x:v>53200</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H6" s="11" t="s">
-        <x:v>66</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
@@ -1644,10 +1647,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>77</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C7" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D7" s="9">
         <x:v>1332000</x:v>
@@ -1659,10 +1662,10 @@
         <x:v>66600</x:v>
       </x:c>
       <x:c r="G7" s="10" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H7" s="11" t="s">
-        <x:v>66</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
@@ -1670,10 +1673,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="8" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C8" s="8" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D8" s="9">
         <x:v>168000</x:v>
@@ -1685,10 +1688,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G8" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H8" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:8">
@@ -1696,10 +1699,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C9" s="8" t="s">
-        <x:v>110</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D9" s="9">
         <x:v>168000</x:v>
@@ -1711,10 +1714,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G9" s="10" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H9" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
@@ -1722,10 +1725,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="8" t="s">
-        <x:v>108</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C10" s="8" t="s">
-        <x:v>96</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D10" s="9">
         <x:v>168000</x:v>
@@ -1740,7 +1743,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:8">
@@ -1748,10 +1751,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>86</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C11" s="8" t="s">
-        <x:v>104</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D11" s="9">
         <x:v>168000</x:v>
@@ -1763,10 +1766,10 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="G11" s="10" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H11" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:8">
@@ -1774,10 +1777,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="8" t="s">
-        <x:v>91</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C12" s="8" t="s">
-        <x:v>80</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D12" s="9">
         <x:v>168000</x:v>
@@ -1789,10 +1792,10 @@
         <x:v>6700</x:v>
       </x:c>
       <x:c r="G12" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H12" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:8">
@@ -1800,10 +1803,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="7" t="s">
-        <x:v>105</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C13" s="8" t="s">
-        <x:v>93</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D13" s="9">
         <x:v>168000</x:v>
@@ -1815,10 +1818,10 @@
         <x:v>8400</x:v>
       </x:c>
       <x:c r="G13" s="10" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H13" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:8">
@@ -1826,10 +1829,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="8" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C14" s="8" t="s">
-        <x:v>107</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D14" s="9">
         <x:v>667000</x:v>
@@ -1841,10 +1844,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G14" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H14" s="11" t="s">
-        <x:v>103</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:8">
@@ -1852,10 +1855,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="7" t="s">
-        <x:v>106</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C15" s="8" t="s">
-        <x:v>102</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D15" s="9">
         <x:v>667000</x:v>
@@ -1867,10 +1870,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G15" s="10" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H15" s="11" t="s">
-        <x:v>103</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:8">
@@ -1878,10 +1881,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>88</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D16" s="9">
         <x:v>667000</x:v>
@@ -1893,10 +1896,10 @@
         <x:v>13300</x:v>
       </x:c>
       <x:c r="G16" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H16" s="11" t="s">
-        <x:v>103</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:8">
@@ -1904,10 +1907,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="7" t="s">
-        <x:v>87</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C17" s="8" t="s">
-        <x:v>85</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D17" s="9">
         <x:v>667000</x:v>
@@ -1919,10 +1922,10 @@
         <x:v>20000</x:v>
       </x:c>
       <x:c r="G17" s="10" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H17" s="11" t="s">
-        <x:v>103</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:8">
@@ -1930,10 +1933,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>109</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
-        <x:v>79</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D18" s="9">
         <x:v>667000</x:v>
@@ -1945,10 +1948,10 @@
         <x:v>26600</x:v>
       </x:c>
       <x:c r="G18" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H18" s="11" t="s">
-        <x:v>103</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8">
@@ -1956,10 +1959,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>98</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D19" s="9">
         <x:v>667000</x:v>
@@ -1971,10 +1974,10 @@
         <x:v>33300</x:v>
       </x:c>
       <x:c r="G19" s="10" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H19" s="11" t="s">
-        <x:v>103</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:8">
@@ -1982,10 +1985,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="8" t="s">
-        <x:v>89</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C20" s="8" t="s">
-        <x:v>81</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D20" s="9">
         <x:v>335000</x:v>
@@ -1997,10 +2000,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G20" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H20" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:8">
@@ -2008,10 +2011,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C21" s="8" t="s">
-        <x:v>95</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D21" s="9">
         <x:v>335000</x:v>
@@ -2023,10 +2026,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G21" s="10" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H21" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:8">
@@ -2034,10 +2037,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="8" t="s">
-        <x:v>99</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C22" s="8" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D22" s="9">
         <x:v>335000</x:v>
@@ -2049,10 +2052,10 @@
         <x:v>6700</x:v>
       </x:c>
       <x:c r="G22" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H22" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:8">
@@ -2060,10 +2063,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="7" t="s">
-        <x:v>83</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
-        <x:v>100</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D23" s="9">
         <x:v>335000</x:v>
@@ -2075,10 +2078,10 @@
         <x:v>10000</x:v>
       </x:c>
       <x:c r="G23" s="10" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H23" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:8">
@@ -2086,10 +2089,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="8" t="s">
-        <x:v>101</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C24" s="8" t="s">
-        <x:v>137</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D24" s="9">
         <x:v>335000</x:v>
@@ -2101,10 +2104,10 @@
         <x:v>13400</x:v>
       </x:c>
       <x:c r="G24" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H24" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:8">
@@ -2112,10 +2115,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="7" t="s">
-        <x:v>138</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C25" s="8" t="s">
-        <x:v>132</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D25" s="9">
         <x:v>335000</x:v>
@@ -2127,10 +2130,10 @@
         <x:v>16700</x:v>
       </x:c>
       <x:c r="G25" s="10" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H25" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:8">
@@ -2138,10 +2141,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="8" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C26" s="8" t="s">
-        <x:v>6</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D26" s="9">
         <x:v>335000</x:v>
@@ -2153,10 +2156,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G26" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H26" s="11" t="s">
-        <x:v>112</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:8">
@@ -2164,10 +2167,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="7" t="s">
-        <x:v>139</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C27" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D27" s="9">
         <x:v>335000</x:v>
@@ -2179,10 +2182,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G27" s="10" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H27" s="11" t="s">
-        <x:v>112</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:8">
@@ -2190,10 +2193,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="8" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C28" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D28" s="9">
         <x:v>335000</x:v>
@@ -2205,10 +2208,10 @@
         <x:v>6700</x:v>
       </x:c>
       <x:c r="G28" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H28" s="11" t="s">
-        <x:v>112</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:8">
@@ -2216,10 +2219,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C29" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D29" s="9">
         <x:v>335000</x:v>
@@ -2231,10 +2234,10 @@
         <x:v>10000</x:v>
       </x:c>
       <x:c r="G29" s="10" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H29" s="11" t="s">
         <x:v>167</x:v>
-      </x:c>
-      <x:c r="H29" s="11" t="s">
-        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:8">
@@ -2242,10 +2245,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="8" t="s">
-        <x:v>131</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C30" s="8" t="s">
-        <x:v>9</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D30" s="9">
         <x:v>335000</x:v>
@@ -2257,10 +2260,10 @@
         <x:v>13400</x:v>
       </x:c>
       <x:c r="G30" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H30" s="11" t="s">
-        <x:v>112</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:8">
@@ -2268,10 +2271,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="7" t="s">
-        <x:v>111</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C31" s="8" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D31" s="9">
         <x:v>335000</x:v>
@@ -2283,10 +2286,10 @@
         <x:v>16700</x:v>
       </x:c>
       <x:c r="G31" s="10" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H31" s="11" t="s">
-        <x:v>112</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:8">
@@ -2294,10 +2297,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="8" t="s">
-        <x:v>141</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C32" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D32" s="9">
         <x:v>1216000</x:v>
@@ -2309,10 +2312,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G32" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H32" s="11" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:8">
@@ -2323,7 +2326,7 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="C33" s="8" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D33" s="9">
         <x:v>1216000</x:v>
@@ -2335,10 +2338,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G33" s="10" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H33" s="11" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:8">
@@ -2346,10 +2349,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="8" t="s">
-        <x:v>128</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C34" s="8" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D34" s="9">
         <x:v>1216000</x:v>
@@ -2361,10 +2364,10 @@
         <x:v>24300</x:v>
       </x:c>
       <x:c r="G34" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H34" s="11" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:8">
@@ -2372,10 +2375,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="7" t="s">
-        <x:v>136</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C35" s="8" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D35" s="9">
         <x:v>1216000</x:v>
@@ -2387,10 +2390,10 @@
         <x:v>36400</x:v>
       </x:c>
       <x:c r="G35" s="10" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H35" s="11" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:8">
@@ -2398,10 +2401,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="8" t="s">
-        <x:v>127</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C36" s="8" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D36" s="9">
         <x:v>1216000</x:v>
@@ -2413,10 +2416,10 @@
         <x:v>48600</x:v>
       </x:c>
       <x:c r="G36" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H36" s="11" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:8">
@@ -2424,10 +2427,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="7" t="s">
-        <x:v>119</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C37" s="8" t="s">
-        <x:v>14</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D37" s="9">
         <x:v>1216000</x:v>
@@ -2439,10 +2442,10 @@
         <x:v>60800</x:v>
       </x:c>
       <x:c r="G37" s="10" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H37" s="11" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:8">
@@ -2450,10 +2453,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="8" t="s">
-        <x:v>142</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C38" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D38" s="9">
         <x:v>4540000</x:v>
@@ -2465,10 +2468,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G38" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H38" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:8">
@@ -2476,10 +2479,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="7" t="s">
-        <x:v>130</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C39" s="8" t="s">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D39" s="9">
         <x:v>4540000</x:v>
@@ -2491,10 +2494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G39" s="10" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H39" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:8">
@@ -2502,10 +2505,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="8" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C40" s="8" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D40" s="9">
         <x:v>4540000</x:v>
@@ -2517,10 +2520,10 @@
         <x:v>90800</x:v>
       </x:c>
       <x:c r="G40" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H40" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:8">
@@ -2528,10 +2531,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="7" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C41" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="9">
         <x:v>4540000</x:v>
@@ -2543,10 +2546,10 @@
         <x:v>136200</x:v>
       </x:c>
       <x:c r="G41" s="10" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H41" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:8">
@@ -2554,10 +2557,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="8" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C42" s="8" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D42" s="9">
         <x:v>4540000</x:v>
@@ -2569,10 +2572,10 @@
         <x:v>181600</x:v>
       </x:c>
       <x:c r="G42" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H42" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:8">
@@ -2580,10 +2583,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="7" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C43" s="8" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D43" s="9">
         <x:v>4540000</x:v>
@@ -2595,10 +2598,10 @@
         <x:v>227000</x:v>
       </x:c>
       <x:c r="G43" s="10" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H43" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:8">
@@ -2606,10 +2609,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C44" s="8" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D44" s="9">
         <x:v>1332000</x:v>
@@ -2621,10 +2624,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G44" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H44" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:8">
@@ -2632,10 +2635,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C45" s="8" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D45" s="9">
         <x:v>1332000</x:v>
@@ -2647,10 +2650,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G45" s="10" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H45" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:8">
@@ -2658,10 +2661,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="8" t="s">
-        <x:v>122</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C46" s="8" t="s">
-        <x:v>24</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D46" s="9">
         <x:v>1332000</x:v>
@@ -2673,10 +2676,10 @@
         <x:v>26600</x:v>
       </x:c>
       <x:c r="G46" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H46" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:8">
@@ -2684,10 +2687,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C47" s="8" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D47" s="9">
         <x:v>1332000</x:v>
@@ -2699,10 +2702,10 @@
         <x:v>39900</x:v>
       </x:c>
       <x:c r="G47" s="10" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H47" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:8">
@@ -2710,10 +2713,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="8" t="s">
-        <x:v>124</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C48" s="8" t="s">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D48" s="9">
         <x:v>1332000</x:v>
@@ -2725,10 +2728,10 @@
         <x:v>53200</x:v>
       </x:c>
       <x:c r="G48" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H48" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:8">
@@ -2736,10 +2739,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="7" t="s">
-        <x:v>129</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C49" s="8" t="s">
-        <x:v>21</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D49" s="9">
         <x:v>1332000</x:v>
@@ -2751,10 +2754,10 @@
         <x:v>66600</x:v>
       </x:c>
       <x:c r="G49" s="10" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H49" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:8">
@@ -2762,10 +2765,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C50" s="8" t="s">
-        <x:v>26</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D50" s="9">
         <x:v>335000</x:v>
@@ -2777,10 +2780,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G50" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H50" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:8">
@@ -2788,10 +2791,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="7" t="s">
-        <x:v>126</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C51" s="8" t="s">
-        <x:v>31</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D51" s="9">
         <x:v>335000</x:v>
@@ -2803,10 +2806,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G51" s="10" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H51" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:8">
@@ -2814,10 +2817,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B52" s="8" t="s">
-        <x:v>144</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C52" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D52" s="9">
         <x:v>335000</x:v>
@@ -2829,10 +2832,10 @@
         <x:v>6700</x:v>
       </x:c>
       <x:c r="G52" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H52" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:8">
@@ -2840,10 +2843,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B53" s="7" t="s">
-        <x:v>157</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C53" s="8" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D53" s="9">
         <x:v>335000</x:v>
@@ -2855,10 +2858,10 @@
         <x:v>10000</x:v>
       </x:c>
       <x:c r="G53" s="10" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H53" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:8">
@@ -2866,10 +2869,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B54" s="8" t="s">
-        <x:v>146</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C54" s="8" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D54" s="9">
         <x:v>335000</x:v>
@@ -2881,10 +2884,10 @@
         <x:v>13400</x:v>
       </x:c>
       <x:c r="G54" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H54" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:8">
@@ -2892,10 +2895,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B55" s="7" t="s">
-        <x:v>154</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C55" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D55" s="9">
         <x:v>335000</x:v>
@@ -2907,10 +2910,10 @@
         <x:v>16700</x:v>
       </x:c>
       <x:c r="G55" s="10" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H55" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:8">
@@ -2918,10 +2921,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B56" s="8" t="s">
-        <x:v>160</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C56" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D56" s="9">
         <x:v>4540000</x:v>
@@ -2933,10 +2936,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G56" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H56" s="11" t="s">
-        <x:v>155</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:8">
@@ -2944,10 +2947,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B57" s="7" t="s">
-        <x:v>161</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C57" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D57" s="9">
         <x:v>4540000</x:v>
@@ -2959,10 +2962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G57" s="10" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H57" s="11" t="s">
-        <x:v>155</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:8">
@@ -2970,10 +2973,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B58" s="8" t="s">
-        <x:v>143</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C58" s="8" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D58" s="9">
         <x:v>4540000</x:v>
@@ -2985,10 +2988,10 @@
         <x:v>90800</x:v>
       </x:c>
       <x:c r="G58" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H58" s="11" t="s">
-        <x:v>155</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:8">
@@ -2996,10 +2999,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B59" s="7" t="s">
-        <x:v>147</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C59" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D59" s="9">
         <x:v>4540000</x:v>
@@ -3011,10 +3014,10 @@
         <x:v>136200</x:v>
       </x:c>
       <x:c r="G59" s="10" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H59" s="11" t="s">
-        <x:v>155</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:8">
@@ -3022,10 +3025,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B60" s="8" t="s">
-        <x:v>166</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C60" s="8" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D60" s="9">
         <x:v>4540000</x:v>
@@ -3037,10 +3040,10 @@
         <x:v>181600</x:v>
       </x:c>
       <x:c r="G60" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H60" s="11" t="s">
-        <x:v>155</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:8">
@@ -3048,10 +3051,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B61" s="7" t="s">
-        <x:v>149</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C61" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D61" s="9">
         <x:v>4540000</x:v>
@@ -3063,10 +3066,10 @@
         <x:v>227000</x:v>
       </x:c>
       <x:c r="G61" s="10" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H61" s="11" t="s">
-        <x:v>155</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:8">
@@ -3074,10 +3077,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B62" s="8" t="s">
-        <x:v>148</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C62" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D62" s="9">
         <x:v>1332000</x:v>
@@ -3089,10 +3092,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G62" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H62" s="11" t="s">
-        <x:v>162</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:8">
@@ -3100,10 +3103,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B63" s="7" t="s">
-        <x:v>150</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C63" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D63" s="9">
         <x:v>1332000</x:v>
@@ -3115,10 +3118,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G63" s="10" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H63" s="11" t="s">
-        <x:v>162</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:8">
@@ -3126,10 +3129,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B64" s="8" t="s">
-        <x:v>163</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C64" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D64" s="9">
         <x:v>1332000</x:v>
@@ -3141,10 +3144,10 @@
         <x:v>26600</x:v>
       </x:c>
       <x:c r="G64" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H64" s="11" t="s">
-        <x:v>162</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:8">
@@ -3152,10 +3155,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B65" s="7" t="s">
-        <x:v>151</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C65" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D65" s="9">
         <x:v>1332000</x:v>
@@ -3167,10 +3170,10 @@
         <x:v>39900</x:v>
       </x:c>
       <x:c r="G65" s="10" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H65" s="11" t="s">
-        <x:v>162</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:8">
@@ -3178,10 +3181,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B66" s="8" t="s">
-        <x:v>152</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C66" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D66" s="9">
         <x:v>1332000</x:v>
@@ -3193,10 +3196,10 @@
         <x:v>53200</x:v>
       </x:c>
       <x:c r="G66" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H66" s="11" t="s">
-        <x:v>162</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:8">
@@ -3204,10 +3207,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B67" s="7" t="s">
-        <x:v>153</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C67" s="8" t="s">
-        <x:v>48</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D67" s="9">
         <x:v>1332000</x:v>
@@ -3219,10 +3222,10 @@
         <x:v>66600</x:v>
       </x:c>
       <x:c r="G67" s="10" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H67" s="11" t="s">
-        <x:v>162</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:8">
@@ -3230,10 +3233,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" s="8" t="s">
-        <x:v>159</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C68" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D68" s="9">
         <x:v>335000</x:v>
@@ -3245,10 +3248,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G68" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H68" s="11" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:8">
@@ -3256,10 +3259,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B69" s="7" t="s">
-        <x:v>145</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C69" s="8" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D69" s="9">
         <x:v>335000</x:v>
@@ -3271,10 +3274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G69" s="10" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H69" s="11" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:8">
@@ -3282,10 +3285,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B70" s="8" t="s">
-        <x:v>156</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C70" s="8" t="s">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D70" s="9">
         <x:v>335000</x:v>
@@ -3297,10 +3300,10 @@
         <x:v>6700</x:v>
       </x:c>
       <x:c r="G70" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H70" s="11" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:8">
@@ -3308,10 +3311,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B71" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C71" s="8" t="s">
-        <x:v>3</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D71" s="9">
         <x:v>335000</x:v>
@@ -3323,10 +3326,10 @@
         <x:v>10000</x:v>
       </x:c>
       <x:c r="G71" s="10" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H71" s="11" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:8">
@@ -3334,10 +3337,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B72" s="8" t="s">
-        <x:v>158</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C72" s="8" t="s">
-        <x:v>1</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D72" s="9">
         <x:v>335000</x:v>
@@ -3349,10 +3352,10 @@
         <x:v>13400</x:v>
       </x:c>
       <x:c r="G72" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H72" s="11" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:8">
@@ -3360,10 +3363,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B73" s="7" t="s">
-        <x:v>165</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C73" s="8" t="s">
-        <x:v>2</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D73" s="9">
         <x:v>335000</x:v>
@@ -3375,14 +3378,14 @@
         <x:v>16700</x:v>
       </x:c>
       <x:c r="G73" s="10" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H73" s="11" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>